--- a/testData/OpenCart_LoginData.xlsx
+++ b/testData/OpenCart_LoginData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>username</t>
   </si>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.88671875" customWidth="1"/>
@@ -448,6 +448,11 @@
       </c>
       <c r="C5" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
